--- a/tests/fixtures/sample_visits.xlsx
+++ b/tests/fixtures/sample_visits.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
